--- a/survey_templates/047_philosophical_insights_on_study--survey_templates.xlsx
+++ b/survey_templates/047_philosophical_insights_on_study--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>study_motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,30 +577,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>study_goal</t>
+          <t>select_one_study_goal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Study Goal</t>
+          <t>Select One Study Goal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,478 +612,317 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>study_duration</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Study Duration</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>study_start_date</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Study Start Date</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>study_finish_date</t>
+          <t>study_duration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Study Finish Date</t>
+          <t>Study Duration</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>select_one_study_purpose</t>
+          <t>select_multiple_study_goal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Select One Study Purpose</t>
+          <t>Select Multiple Study Goals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>select_multiple_study_motivation</t>
+          <t>study_start_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select Multiple Motivation</t>
+          <t>Study Start Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_one_study_goal</t>
+          <t>study_finish_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select One Study Goal</t>
+          <t>Study Finish Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>study_duration_range</t>
+          <t>study_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Study Duration Range</t>
+          <t>Study Time</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_one_personals_growth</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select One Personal Growth</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>select_one_survey_goal_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contact Email</t>
+          <t>Select One Survey Goal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>study_goal_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
+          <t>Study Goal 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one_survey_goal_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Study Time</t>
+          <t>Select One Survey Goal 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one_survey_goal_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Study Date</t>
+          <t>Select One Survey Goal 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one_survey_goal_6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Select One Survey Goal 6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select_one_survey_goal_2</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select One Survey Goal</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Select One Survey Goal</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Select One Survey Goal</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Select One Survey Goal</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Select One Survey Goal</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select One Survey Goal</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_8</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select One Survey Goal</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_9</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Select One Survey Goal</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,663 +965,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one_study_purpose_choices</t>
+          <t>select_one_study_goal_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>study_for_fun</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Study for Fun</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_one_study_purpose_choices</t>
+          <t>select_one_study_goal_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>personal_growth</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Personal Growth</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one_study_purpose_choices</t>
+          <t>select_one_study_goal_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>career_development</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Career Development</t>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple_study_motivation_choices</t>
+          <t>select_multiple_study_goal_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>motivation_1</t>
+          <t>goal_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Motivation 1</t>
+          <t>Goal 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple_study_motivation_choices</t>
+          <t>select_multiple_study_goal_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>motivation_2</t>
+          <t>goal_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Motivation 2</t>
+          <t>Goal 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple_study_motivation_choices</t>
+          <t>select_multiple_study_goal_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>motivation_3</t>
+          <t>goal_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Motivation 3</t>
+          <t>Goal 6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_study_goal_choices</t>
+          <t>select_one_survey_goal_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>goal_1</t>
+          <t>goal_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Goal 1</t>
+          <t>Goal 7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_study_goal_choices</t>
+          <t>select_one_survey_goal_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>goal_2</t>
+          <t>goal_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Goal 2</t>
+          <t>Goal 8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_study_goal_choices</t>
+          <t>select_one_survey_goal_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>goal_3</t>
+          <t>goal_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Goal 3</t>
+          <t>Goal 9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>study_duration_range_choices</t>
+          <t>study_goal_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>less_than_1_month</t>
+          <t>goal_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Less than 1 month</t>
+          <t>Goal 10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>study_duration_range_choices</t>
+          <t>study_goal_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1-3_months</t>
+          <t>goal_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1-3 months</t>
+          <t>Goal 11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>study_duration_range_choices</t>
+          <t>study_goal_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4-6_months</t>
+          <t>goal_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4-6 months</t>
+          <t>Goal 12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_personals_growth_choices</t>
+          <t>select_one_survey_goal_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>growth_1</t>
+          <t>goal_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Growth 1</t>
+          <t>Goal 13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one_personals_growth_choices</t>
+          <t>select_one_survey_goal_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>growth_2</t>
+          <t>goal_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Growth 2</t>
+          <t>Goal 14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one_personals_growth_choices</t>
+          <t>select_one_survey_goal_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>growth_3</t>
+          <t>goal_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Growth 3</t>
+          <t>Goal 15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_survey_goal_2_choices</t>
+          <t>select_one_survey_goal_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>goal_4</t>
+          <t>goal_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goal 4</t>
+          <t>Goal 16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one_survey_goal_2_choices</t>
+          <t>select_one_survey_goal_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>goal_5</t>
+          <t>goal_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal 5</t>
+          <t>Goal 17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_survey_goal_2_choices</t>
+          <t>select_one_survey_goal_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>goal_6</t>
+          <t>goal_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal 6</t>
+          <t>Goal 18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one_survey_goal_3_choices</t>
+          <t>select_one_survey_goal_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>goal_7</t>
+          <t>goal_19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Goal 7</t>
+          <t>Goal 19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_survey_goal_3_choices</t>
+          <t>select_one_survey_goal_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>goal_8</t>
+          <t>goal_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Goal 8</t>
+          <t>Goal 20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_survey_goal_3_choices</t>
+          <t>select_one_survey_goal_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>goal_9</t>
+          <t>goal_21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Goal 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_4_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>goal_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Goal 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_4_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>goal_11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Goal 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_4_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>goal_12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Goal 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_5_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>goal_13</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Goal 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_5_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>goal_14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Goal 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>goal_15</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Goal 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_6_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>goal_16</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Goal 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_6_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>goal_17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Goal 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_6_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>goal_18</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Goal 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_7_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>goal_19</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Goal 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_7_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>goal_20</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Goal 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_7_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>goal_21</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>Goal 21</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_8_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>goal_22</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Goal 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_8_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>goal_23</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Goal 23</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_8_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>goal_24</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Goal 24</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_9_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>goal_25</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Goal 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_9_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>goal_26</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Goal 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_one_survey_goal_9_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>goal_27</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Goal 27</t>
         </is>
       </c>
     </row>
